--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LOBE HUESCA LA MAGIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LOBE HUESCA LA MAGIA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>36.4095</v>
+        <v>41.0362</v>
       </c>
       <c r="E2" t="n">
-        <v>28.123</v>
+        <v>47.7539</v>
       </c>
       <c r="F2" t="n">
-        <v>8.286299999999999</v>
+        <v>-6.7179</v>
       </c>
       <c r="G2" t="n">
-        <v>10.1601</v>
+        <v>10.391</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5593</v>
+        <v>9.914100000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.601</v>
+        <v>0.4766000000000004</v>
       </c>
       <c r="J2" t="n">
-        <v>36.6687</v>
+        <v>47.6353</v>
       </c>
       <c r="K2" t="n">
-        <v>25.1103</v>
+        <v>29.8929</v>
       </c>
       <c r="L2" t="n">
-        <v>11.5582</v>
+        <v>17.7424</v>
       </c>
       <c r="M2" t="n">
-        <v>-26.5086</v>
+        <v>-37.2445</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.5513</v>
+        <v>-19.9788</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.957000000000001</v>
+        <v>-17.266</v>
       </c>
       <c r="P2" t="n">
-        <v>7.3924</v>
+        <v>4.9282</v>
       </c>
       <c r="Q2" t="n">
-        <v>-30.8012</v>
+        <v>-37.988</v>
       </c>
       <c r="R2" t="n">
-        <v>38.1936</v>
+        <v>42.9164</v>
       </c>
       <c r="S2" t="n">
-        <v>14.2594</v>
+        <v>-1.7234</v>
       </c>
       <c r="T2" t="n">
-        <v>5.0978</v>
+        <v>-3.1038</v>
       </c>
       <c r="U2" t="n">
-        <v>9.1615</v>
+        <v>1.3806</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5974</v>
+        <v>27.4404</v>
       </c>
       <c r="W2" t="n">
-        <v>17.1576</v>
+        <v>41.2104</v>
       </c>
       <c r="X2" t="n">
-        <v>-12.5601</v>
+        <v>-13.7704</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>24.884</v>
+        <v>30.0517</v>
       </c>
       <c r="E3" t="n">
-        <v>16.3521</v>
+        <v>24.8727</v>
       </c>
       <c r="F3" t="n">
-        <v>8.531700000000001</v>
+        <v>5.1791</v>
       </c>
       <c r="G3" t="n">
-        <v>6.334099999999999</v>
+        <v>10.1601</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.503400000000001</v>
+        <v>8.5593</v>
       </c>
       <c r="I3" t="n">
-        <v>7.837400000000001</v>
+        <v>1.601</v>
       </c>
       <c r="J3" t="n">
-        <v>26.1615</v>
+        <v>36.6687</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0758</v>
+        <v>25.1103</v>
       </c>
       <c r="L3" t="n">
-        <v>14.0855</v>
+        <v>11.5582</v>
       </c>
       <c r="M3" t="n">
-        <v>-19.8271</v>
+        <v>-26.5086</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.5792</v>
+        <v>-16.5513</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.2481</v>
+        <v>-9.957000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.0803</v>
+        <v>7.3924</v>
       </c>
       <c r="Q3" t="n">
-        <v>-41.0683</v>
+        <v>-30.8012</v>
       </c>
       <c r="R3" t="n">
-        <v>37.9881</v>
+        <v>38.1936</v>
       </c>
       <c r="S3" t="n">
-        <v>11.6011</v>
+        <v>7.9017</v>
       </c>
       <c r="T3" t="n">
-        <v>5.3895</v>
+        <v>1.8476</v>
       </c>
       <c r="U3" t="n">
-        <v>6.2114</v>
+        <v>6.054</v>
       </c>
       <c r="V3" t="n">
-        <v>10.029</v>
+        <v>4.5974</v>
       </c>
       <c r="W3" t="n">
-        <v>25.8696</v>
+        <v>17.1576</v>
       </c>
       <c r="X3" t="n">
-        <v>-15.8411</v>
+        <v>-12.5601</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>24.3331</v>
+        <v>20.9553</v>
       </c>
       <c r="E4" t="n">
-        <v>37.75850000000001</v>
+        <v>14.7485</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.4253</v>
+        <v>6.2071</v>
       </c>
       <c r="G4" t="n">
-        <v>10.391</v>
+        <v>6.334099999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>9.914100000000001</v>
+        <v>-1.503400000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4766000000000004</v>
+        <v>7.837400000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>47.6353</v>
+        <v>26.1615</v>
       </c>
       <c r="K4" t="n">
-        <v>29.8929</v>
+        <v>12.0758</v>
       </c>
       <c r="L4" t="n">
-        <v>17.7424</v>
+        <v>14.0855</v>
       </c>
       <c r="M4" t="n">
-        <v>-37.2445</v>
+        <v>-19.8271</v>
       </c>
       <c r="N4" t="n">
-        <v>-19.9788</v>
+        <v>-13.5792</v>
       </c>
       <c r="O4" t="n">
-        <v>-17.266</v>
+        <v>-6.2481</v>
       </c>
       <c r="P4" t="n">
-        <v>4.9282</v>
+        <v>-3.0803</v>
       </c>
       <c r="Q4" t="n">
-        <v>-37.988</v>
+        <v>-41.0683</v>
       </c>
       <c r="R4" t="n">
-        <v>42.9164</v>
+        <v>37.9881</v>
       </c>
       <c r="S4" t="n">
-        <v>-18.4263</v>
+        <v>7.672599999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-13.0993</v>
+        <v>3.7857</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.3269</v>
+        <v>3.887</v>
       </c>
       <c r="V4" t="n">
-        <v>27.4404</v>
+        <v>10.029</v>
       </c>
       <c r="W4" t="n">
-        <v>41.2104</v>
+        <v>25.8696</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.7704</v>
+        <v>-15.8411</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>6.266799999999999</v>
+        <v>11.8009</v>
       </c>
       <c r="E5" t="n">
-        <v>4.356399999999998</v>
+        <v>5.092400000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9103</v>
+        <v>6.7086</v>
       </c>
       <c r="G5" t="n">
         <v>11.3381</v>
@@ -844,13 +844,13 @@
         <v>27.7212</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.714</v>
+        <v>2.8208</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09010000000000029</v>
+        <v>0.8264</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.8039</v>
+        <v>1.9945</v>
       </c>
       <c r="V5" t="n">
         <v>6.061500000000001</v>
@@ -877,13 +877,13 @@
         <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8454</v>
+        <v>7.6753</v>
       </c>
       <c r="E6" t="n">
-        <v>14.0344</v>
+        <v>15.0184</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.1891</v>
+        <v>-7.3432</v>
       </c>
       <c r="G6" t="n">
         <v>1.3261</v>
@@ -922,13 +922,13 @@
         <v>26.6944</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1271</v>
+        <v>4.9573</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2680999999999996</v>
+        <v>1.2523</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8593</v>
+        <v>3.7051</v>
       </c>
       <c r="V6" t="n">
         <v>-1.072</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>J. WELLS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4084</v>
+        <v>4.5407</v>
       </c>
       <c r="E7" t="n">
-        <v>7.295199999999999</v>
+        <v>12.508</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.8868</v>
+        <v>-7.9673</v>
       </c>
       <c r="G7" t="n">
-        <v>4.0281</v>
+        <v>6.7729</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0755</v>
+        <v>-0.5683999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.952600000000001</v>
+        <v>7.3414</v>
       </c>
       <c r="J7" t="n">
-        <v>13.2243</v>
+        <v>15.5301</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2931</v>
+        <v>5.6013</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9314</v>
+        <v>9.928699999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-9.196200000000001</v>
+        <v>-8.757099999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.2173</v>
+        <v>-6.17</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.979</v>
+        <v>-2.5873</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6428</v>
+        <v>-5.1337</v>
       </c>
       <c r="Q7" t="n">
-        <v>-14.5791</v>
+        <v>-11.2937</v>
       </c>
       <c r="R7" t="n">
-        <v>12.9366</v>
+        <v>6.1604</v>
       </c>
       <c r="S7" t="n">
-        <v>7.5053</v>
+        <v>0.7370000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>7.4489</v>
+        <v>0.9596000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.05640000000000001</v>
+        <v>-0.2227999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.482600000000001</v>
+        <v>2.1643</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2011</v>
+        <v>7.311900000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.6836</v>
+        <v>-5.147600000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RUBIN DE CELIS FERRANDO</t>
+          <t>I. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6535</v>
+        <v>3.4927</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4408</v>
+        <v>3.851</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2126</v>
+        <v>-0.3583999999999997</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5618</v>
+        <v>2.559</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3249</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8867</v>
+        <v>1.5603</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2418</v>
+        <v>2.6681</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0317</v>
+        <v>1.5767</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2101</v>
+        <v>1.0913</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6799000000000001</v>
+        <v>-0.109</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3566</v>
+        <v>-0.578</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6766999999999999</v>
+        <v>0.469</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1068</v>
+        <v>-1.232</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0534</v>
+        <v>3.0802</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00539999999999996</v>
+        <v>0.04659999999999997</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1663</v>
+        <v>-0.1824000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1609</v>
+        <v>0.2288</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1396</v>
+        <v>-0.9610000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1396</v>
+        <v>2.5975</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.5585</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. TERREROS RIVAS</t>
+          <t>A. RUBIN DE CELIS FERRANDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3149</v>
+        <v>2.5104</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6733</v>
+        <v>1.3362</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3583</v>
+        <v>1.1742</v>
       </c>
       <c r="G9" t="n">
-        <v>2.559</v>
+        <v>2.5618</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9987999999999999</v>
+        <v>-0.3249</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5603</v>
+        <v>2.8867</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6681</v>
+        <v>3.2418</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5767</v>
+        <v>1.0317</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0913</v>
+        <v>2.2101</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.109</v>
+        <v>-0.6799000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.578</v>
+        <v>-1.3566</v>
       </c>
       <c r="O9" t="n">
-        <v>0.469</v>
+        <v>0.6766999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8481</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.232</v>
+        <v>-4.1068</v>
       </c>
       <c r="R9" t="n">
-        <v>3.0802</v>
+        <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1312</v>
+        <v>-0.1375</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3602</v>
+        <v>0.06169999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>0.229</v>
+        <v>-0.1993</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9610000000000001</v>
+        <v>2.1396</v>
       </c>
       <c r="W9" t="n">
-        <v>2.5975</v>
+        <v>2.1396</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.5585</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. WELLS</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2064000000000001</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="E10" t="n">
-        <v>9.6294</v>
+        <v>2.890300000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.4231</v>
+        <v>-2.4902</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7729</v>
+        <v>4.0281</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5683999999999999</v>
+        <v>2.0755</v>
       </c>
       <c r="I10" t="n">
-        <v>7.3414</v>
+        <v>1.952600000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>15.5301</v>
+        <v>13.2243</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6013</v>
+        <v>6.2931</v>
       </c>
       <c r="L10" t="n">
-        <v>9.928699999999999</v>
+        <v>6.9314</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.757099999999999</v>
+        <v>-9.196200000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.17</v>
+        <v>-4.2173</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5873</v>
+        <v>-4.979</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.1337</v>
+        <v>-1.6428</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.2937</v>
+        <v>-14.5791</v>
       </c>
       <c r="R10" t="n">
-        <v>6.1604</v>
+        <v>12.9366</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.5972</v>
+        <v>4.497</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9189</v>
+        <v>3.0441</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6785</v>
+        <v>1.4532</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1643</v>
+        <v>-6.482600000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>7.311900000000001</v>
+        <v>1.2011</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.147600000000001</v>
+        <v>-7.6836</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.407</v>
+        <v>-1.3181</v>
       </c>
       <c r="E11" t="n">
         <v>-0.1317</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2753</v>
+        <v>-1.1864</v>
       </c>
       <c r="G11" t="n">
         <v>0.2238</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2119</v>
+        <v>-0.123</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4189</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.843200000000001</v>
+        <v>-1.773400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.7209</v>
+        <v>-0.9022999999999994</v>
       </c>
       <c r="F12" t="n">
-        <v>4.8777</v>
+        <v>-0.8713000000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>-21.3676</v>
+        <v>-13.1306</v>
       </c>
       <c r="H12" t="n">
-        <v>-10.4466</v>
+        <v>-14.2802</v>
       </c>
       <c r="I12" t="n">
-        <v>-10.9214</v>
+        <v>1.1496</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6364</v>
+        <v>1.3471</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2623</v>
+        <v>-4.516900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.8984</v>
+        <v>5.864199999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.7314</v>
+        <v>-14.4778</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.7088</v>
+        <v>-9.763199999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.022499999999999</v>
+        <v>-4.7146</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8214000000000004</v>
+        <v>9.240500000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-29.5691</v>
+        <v>-14.7845</v>
       </c>
       <c r="R12" t="n">
-        <v>28.748</v>
+        <v>24.025</v>
       </c>
       <c r="S12" t="n">
-        <v>15.5795</v>
+        <v>-1.8815</v>
       </c>
       <c r="T12" t="n">
-        <v>13.9016</v>
+        <v>-0.9552000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6782</v>
+        <v>-0.9264</v>
       </c>
       <c r="V12" t="n">
-        <v>1.7664</v>
+        <v>3.9983</v>
       </c>
       <c r="W12" t="n">
-        <v>9.583</v>
+        <v>13.4905</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.8163</v>
+        <v>-9.492000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.923700000000002</v>
+        <v>-9.641400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.826899999999998</v>
+        <v>-15.7066</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0969</v>
+        <v>6.065</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.1306</v>
+        <v>-21.3676</v>
       </c>
       <c r="H13" t="n">
-        <v>-14.2802</v>
+        <v>-10.4466</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1496</v>
+        <v>-10.9214</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3471</v>
+        <v>-3.6364</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.516900000000001</v>
+        <v>1.2623</v>
       </c>
       <c r="L13" t="n">
-        <v>5.864199999999999</v>
+        <v>-4.8984</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.4778</v>
+        <v>-17.7314</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.763199999999999</v>
+        <v>-11.7088</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.7146</v>
+        <v>-6.022499999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>9.240500000000001</v>
+        <v>-0.8214000000000004</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7845</v>
+        <v>-29.5691</v>
       </c>
       <c r="R13" t="n">
-        <v>24.025</v>
+        <v>28.748</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.031700000000001</v>
+        <v>10.7809</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.8796</v>
+        <v>7.916099999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.152</v>
+        <v>2.865</v>
       </c>
       <c r="V13" t="n">
-        <v>3.9983</v>
+        <v>1.7664</v>
       </c>
       <c r="W13" t="n">
-        <v>13.4905</v>
+        <v>9.583</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.492000000000001</v>
+        <v>-7.8163</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.7653</v>
+        <v>-11.3231</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.4867</v>
+        <v>-5.824199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.278600000000001</v>
+        <v>-5.4989</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.8546</v>
+        <v>-7.163400000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-13.6086</v>
+        <v>-5.815300000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>6.7541</v>
+        <v>-1.3477</v>
       </c>
       <c r="J14" t="n">
-        <v>24.1453</v>
+        <v>18.8415</v>
       </c>
       <c r="K14" t="n">
-        <v>8.570600000000001</v>
+        <v>11.8874</v>
       </c>
       <c r="L14" t="n">
-        <v>15.5746</v>
+        <v>6.9538</v>
       </c>
       <c r="M14" t="n">
-        <v>-30.9999</v>
+        <v>-26.0049</v>
       </c>
       <c r="N14" t="n">
-        <v>-22.179</v>
+        <v>-17.703</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.8209</v>
+        <v>-8.3018</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.571</v>
+        <v>-6.1602</v>
       </c>
       <c r="Q14" t="n">
-        <v>-43.9428</v>
+        <v>-33.8815</v>
       </c>
       <c r="R14" t="n">
-        <v>37.3722</v>
+        <v>27.721</v>
       </c>
       <c r="S14" t="n">
-        <v>18.2319</v>
+        <v>5.4621</v>
       </c>
       <c r="T14" t="n">
-        <v>11.9747</v>
+        <v>4.6965</v>
       </c>
       <c r="U14" t="n">
-        <v>6.2575</v>
+        <v>0.7657</v>
       </c>
       <c r="V14" t="n">
-        <v>-20.5717</v>
+        <v>-3.4615</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3364</v>
+        <v>4.5193</v>
       </c>
       <c r="X14" t="n">
-        <v>-21.9082</v>
+        <v>-7.980700000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.2585</v>
+        <v>-16.2808</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.637999999999998</v>
+        <v>-13.9137</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.620699999999999</v>
+        <v>-2.367</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.163400000000001</v>
+        <v>-15.6276</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.815300000000001</v>
+        <v>-10.3707</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3477</v>
+        <v>-5.256500000000002</v>
       </c>
       <c r="J15" t="n">
-        <v>18.8415</v>
+        <v>12.434</v>
       </c>
       <c r="K15" t="n">
-        <v>11.8874</v>
+        <v>8.852600000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>6.9538</v>
+        <v>3.581700000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-26.0049</v>
+        <v>-28.0617</v>
       </c>
       <c r="N15" t="n">
-        <v>-17.703</v>
+        <v>-19.2233</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.3018</v>
+        <v>-8.8385</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.1602</v>
+        <v>-5.749400000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-33.8815</v>
+        <v>-49.6925</v>
       </c>
       <c r="R15" t="n">
-        <v>27.721</v>
+        <v>43.9432</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5266000000000003</v>
+        <v>11.0796</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8828</v>
+        <v>6.0972</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.3562</v>
+        <v>4.9823</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.4615</v>
+        <v>-5.9833</v>
       </c>
       <c r="W15" t="n">
-        <v>4.5193</v>
+        <v>17.2478</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.980700000000001</v>
+        <v>-23.231</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>P. SUÁREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.1801</v>
+        <v>-16.5103</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.8412</v>
+        <v>-11.8711</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3389000000000015</v>
+        <v>-4.6393</v>
       </c>
       <c r="G16" t="n">
-        <v>-15.6276</v>
+        <v>-17.4186</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.3707</v>
+        <v>-9.6046</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.256500000000002</v>
+        <v>-7.8141</v>
       </c>
       <c r="J16" t="n">
-        <v>12.434</v>
+        <v>-4.9973</v>
       </c>
       <c r="K16" t="n">
-        <v>8.852600000000001</v>
+        <v>-0.3873</v>
       </c>
       <c r="L16" t="n">
-        <v>3.581700000000001</v>
+        <v>-4.610000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-28.0617</v>
+        <v>-12.4213</v>
       </c>
       <c r="N16" t="n">
-        <v>-19.2233</v>
+        <v>-9.2173</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.8385</v>
+        <v>-3.204</v>
       </c>
       <c r="P16" t="n">
-        <v>-5.749400000000001</v>
+        <v>8.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>-49.6925</v>
+        <v>-8.6243</v>
       </c>
       <c r="R16" t="n">
-        <v>43.9432</v>
+        <v>17.2489</v>
       </c>
       <c r="S16" t="n">
-        <v>7.1802</v>
+        <v>-0.7576999999999998</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1699000000000002</v>
+        <v>-0.1488999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>7.010599999999999</v>
+        <v>-0.6088</v>
       </c>
       <c r="V16" t="n">
-        <v>-5.9833</v>
+        <v>-6.9585</v>
       </c>
       <c r="W16" t="n">
-        <v>17.2478</v>
+        <v>1.8992</v>
       </c>
       <c r="X16" t="n">
-        <v>-23.231</v>
+        <v>-8.857699999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.7948</v>
+        <v>-23.2271</v>
       </c>
       <c r="E17" t="n">
-        <v>-14.0834</v>
+        <v>-13.4254</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.7112</v>
+        <v>-9.8018</v>
       </c>
       <c r="G17" t="n">
-        <v>-17.4186</v>
+        <v>-6.8546</v>
       </c>
       <c r="H17" t="n">
-        <v>-9.6046</v>
+        <v>-13.6086</v>
       </c>
       <c r="I17" t="n">
-        <v>-7.8141</v>
+        <v>6.7541</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.9973</v>
+        <v>24.1453</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3873</v>
+        <v>8.570600000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-4.610000000000001</v>
+        <v>15.5746</v>
       </c>
       <c r="M17" t="n">
-        <v>-12.4213</v>
+        <v>-30.9999</v>
       </c>
       <c r="N17" t="n">
-        <v>-9.2173</v>
+        <v>-22.179</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.204</v>
+        <v>-8.8209</v>
       </c>
       <c r="P17" t="n">
-        <v>8.6244</v>
+        <v>-6.571</v>
       </c>
       <c r="Q17" t="n">
-        <v>-8.6243</v>
+        <v>-43.9428</v>
       </c>
       <c r="R17" t="n">
-        <v>17.2489</v>
+        <v>37.3722</v>
       </c>
       <c r="S17" t="n">
-        <v>-6.042</v>
+        <v>10.77</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.3612</v>
+        <v>5.0359</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.681</v>
+        <v>5.7339</v>
       </c>
       <c r="V17" t="n">
-        <v>-6.9585</v>
+        <v>-20.5717</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8992</v>
+        <v>1.3364</v>
       </c>
       <c r="X17" t="n">
-        <v>-8.857699999999999</v>
+        <v>-21.9082</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>17.14939999999999</v>
+        <v>42.389</v>
       </c>
       <c r="E18" t="n">
-        <v>59.93430000000002</v>
+        <v>66.29640000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-42.7856</v>
+        <v>-23.90769999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-25.8674</v>
@@ -1846,10 +1846,10 @@
         <v>-175.0997</v>
       </c>
       <c r="O18" t="n">
-        <v>-94.60199999999999</v>
+        <v>-94.602</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.1334</v>
+        <v>-5.133399999999998</v>
       </c>
       <c r="Q18" t="n">
         <v>-381.9339</v>
@@ -1858,13 +1858,13 @@
         <v>376.8026</v>
       </c>
       <c r="S18" t="n">
-        <v>36.8622</v>
+        <v>62.10249999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>24.6388</v>
+        <v>31.0011</v>
       </c>
       <c r="U18" t="n">
-        <v>12.2243</v>
+        <v>31.1015</v>
       </c>
       <c r="V18" t="n">
         <v>11.28740000000001</v>
